--- a/psychopy_exp_files/sequences/learning_block3_fixed-middle-10_50.xlsx
+++ b/psychopy_exp_files/sequences/learning_block3_fixed-middle-10_50.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_38.jpg</t>
+          <t>stimuli/bread/bread_30.jpg</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -594,7 +594,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -638,7 +638,7 @@
         <v>14</v>
       </c>
       <c r="V2" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="W2" t="n">
         <v>13</v>
@@ -772,7 +772,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_34.jpg</t>
+          <t>stimuli/chair/chair_13.jpg</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -792,7 +792,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -836,7 +836,7 @@
         <v>8</v>
       </c>
       <c r="V4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="W4" t="n">
         <v>13</v>
@@ -871,12 +871,12 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_30.jpg</t>
+          <t>stimuli/jacket/jacket_38.jpg</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_34.jpg</t>
+          <t>stimuli/chair/chair_13.jpg</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -891,12 +891,12 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -935,10 +935,10 @@
         <v>7</v>
       </c>
       <c r="V5" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -965,7 +965,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_30.jpg</t>
+          <t>stimuli/jacket/jacket_38.jpg</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -985,7 +985,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1031,7 +1031,7 @@
         <v>7</v>
       </c>
       <c r="U6" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="V6" t="n">
         <v>2</v>
@@ -1059,17 +1059,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
+          <t>stimuli/jacket/jacket_38.jpg</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
           <t>stimuli/flower/flower_30.jpg</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>stimuli/dog/dog_06.jpg</t>
-        </is>
-      </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_13.jpg</t>
+          <t>stimuli/ball/ball_34.jpg</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1079,17 +1079,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
+          <t>jacket</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>flower</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>dog</t>
-        </is>
-      </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1127,13 +1127,13 @@
         <v>7</v>
       </c>
       <c r="T7" t="n">
+        <v>10</v>
+      </c>
+      <c r="U7" t="n">
         <v>6</v>
       </c>
-      <c r="U7" t="n">
-        <v>5</v>
-      </c>
       <c r="V7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="W7" t="n">
         <v>13</v>
@@ -1158,7 +1158,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_06.jpg</t>
+          <t>stimuli/flower/flower_30.jpg</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1168,7 +1168,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_34.jpg</t>
+          <t>stimuli/chair/chair_13.jpg</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1188,7 +1188,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1226,13 +1226,13 @@
         <v>8</v>
       </c>
       <c r="T8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U8" t="n">
         <v>2</v>
       </c>
       <c r="V8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="W8" t="n">
         <v>7</v>
@@ -1262,7 +1262,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_38.jpg</t>
+          <t>stimuli/bread/bread_30.jpg</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1282,7 +1282,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1328,7 +1328,7 @@
         <v>2</v>
       </c>
       <c r="U9" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="V9" t="n">
         <v>13</v>
@@ -1356,12 +1356,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_38.jpg</t>
+          <t>stimuli/bread/bread_30.jpg</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_30.jpg</t>
+          <t>stimuli/dog/dog_06.jpg</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1371,17 +1371,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_06.jpg</t>
+          <t>stimuli/flower/flower_30.jpg</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1391,7 +1391,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1424,16 +1424,16 @@
         <v>10</v>
       </c>
       <c r="T10" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="U10" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="V10" t="n">
         <v>9</v>
       </c>
       <c r="W10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11">
@@ -1455,12 +1455,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_30.jpg</t>
+          <t>stimuli/dog/dog_06.jpg</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_13.jpg</t>
+          <t>stimuli/ball/ball_34.jpg</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1475,12 +1475,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1523,10 +1523,10 @@
         <v>11</v>
       </c>
       <c r="T11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U11" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="V11" t="n">
         <v>14</v>
@@ -1554,14 +1554,14 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
+          <t>stimuli/ball/ball_34.jpg</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
           <t>stimuli/chair/chair_13.jpg</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>stimuli/ball/ball_34.jpg</t>
-        </is>
-      </c>
       <c r="G12" t="inlineStr">
         <is>
           <t>stimuli/fish/fish_40.jpg</t>
@@ -1574,12 +1574,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
+          <t>ball</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
           <t>chair</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>ball</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1622,10 +1622,10 @@
         <v>12</v>
       </c>
       <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
         <v>4</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1</v>
       </c>
       <c r="V12" t="n">
         <v>12</v>
@@ -1653,7 +1653,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_34.jpg</t>
+          <t>stimuli/chair/chair_13.jpg</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_30.jpg</t>
+          <t>stimuli/dog/dog_06.jpg</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1688,7 +1688,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1721,7 +1721,7 @@
         <v>13</v>
       </c>
       <c r="T13" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U13" t="n">
         <v>15</v>
@@ -1730,7 +1730,7 @@
         <v>8</v>
       </c>
       <c r="W13" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14">
@@ -1767,7 +1767,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_06.jpg</t>
+          <t>stimuli/flower/flower_30.jpg</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1787,7 +1787,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1829,7 +1829,7 @@
         <v>14</v>
       </c>
       <c r="W14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_23.jpg</t>
+          <t>stimuli/ball/ball_05.jpg</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1881,7 +1881,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1925,7 +1925,7 @@
         <v>15</v>
       </c>
       <c r="V15" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="W15" t="n">
         <v>11</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_08.jpg</t>
+          <t>stimuli/jacket/jacket_16.jpg</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1975,7 +1975,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -2021,7 +2021,7 @@
         <v>15</v>
       </c>
       <c r="U16" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="V16" t="n">
         <v>9</v>
@@ -2049,17 +2049,17 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_08.jpg</t>
+          <t>stimuli/jacket/jacket_16.jpg</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_05.jpg</t>
+          <t>stimuli/chair/chair_23.jpg</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_16.jpg</t>
+          <t>stimuli/bread/bread_37.jpg</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2069,17 +2069,17 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -2117,13 +2117,13 @@
         <v>4</v>
       </c>
       <c r="T17" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="U17" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="V17" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="W17" t="n">
         <v>16</v>
@@ -2148,7 +2148,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_05.jpg</t>
+          <t>stimuli/chair/chair_23.jpg</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -2158,7 +2158,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_37.jpg</t>
+          <t>stimuli/dog/dog_09.jpg</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2168,7 +2168,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2178,7 +2178,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -2216,13 +2216,13 @@
         <v>5</v>
       </c>
       <c r="T18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U18" t="n">
         <v>2</v>
       </c>
       <c r="V18" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="W18" t="n">
         <v>11</v>
@@ -2351,12 +2351,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_37.jpg</t>
+          <t>stimuli/dog/dog_09.jpg</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_09.jpg</t>
+          <t>stimuli/flower/flower_08.jpg</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2417,10 +2417,10 @@
         <v>9</v>
       </c>
       <c r="U20" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="V20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W20" t="n">
         <v>16</v>
@@ -2445,17 +2445,17 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_37.jpg</t>
+          <t>stimuli/dog/dog_09.jpg</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_09.jpg</t>
+          <t>stimuli/flower/flower_08.jpg</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_08.jpg</t>
+          <t>stimuli/jacket/jacket_16.jpg</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2465,17 +2465,17 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2513,13 +2513,13 @@
         <v>8</v>
       </c>
       <c r="T21" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V21" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W21" t="n">
         <v>2</v>
@@ -2544,7 +2544,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_09.jpg</t>
+          <t>stimuli/flower/flower_08.jpg</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2564,7 +2564,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2612,7 +2612,7 @@
         <v>9</v>
       </c>
       <c r="T22" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U22" t="n">
         <v>7</v>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_23.jpg</t>
+          <t>stimuli/ball/ball_05.jpg</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -2668,7 +2668,7 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -2714,7 +2714,7 @@
         <v>7</v>
       </c>
       <c r="U23" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="V23" t="n">
         <v>11</v>
@@ -2742,42 +2742,42 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
+          <t>stimuli/ball/ball_05.jpg</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>stimuli/bread/bread_37.jpg</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
           <t>stimuli/chair/chair_23.jpg</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>stimuli/jacket/jacket_16.jpg</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>stimuli/ball/ball_05.jpg</t>
-        </is>
-      </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_37.jpg</t>
+          <t>stimuli/dog/dog_09.jpg</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
+          <t>ball</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>bread</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
           <t>chair</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>jacket</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>ball</t>
-        </is>
-      </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -2810,16 +2810,16 @@
         <v>11</v>
       </c>
       <c r="T24" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" t="n">
+        <v>3</v>
+      </c>
+      <c r="V24" t="n">
         <v>4</v>
       </c>
-      <c r="U24" t="n">
-        <v>10</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1</v>
-      </c>
       <c r="W24" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_16.jpg</t>
+          <t>stimuli/bread/bread_37.jpg</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -2856,12 +2856,12 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_05.jpg</t>
+          <t>stimuli/chair/chair_23.jpg</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2909,7 +2909,7 @@
         <v>12</v>
       </c>
       <c r="T25" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="U25" t="n">
         <v>8</v>
@@ -2918,7 +2918,7 @@
         <v>14</v>
       </c>
       <c r="W25" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="26">
@@ -2950,7 +2950,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_08.jpg</t>
+          <t>stimuli/jacket/jacket_16.jpg</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2970,7 +2970,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -3014,7 +3014,7 @@
         <v>16</v>
       </c>
       <c r="V26" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W26" t="n">
         <v>2</v>
@@ -3148,7 +3148,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_13.jpg</t>
+          <t>stimuli/ball/ball_34.jpg</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3168,7 +3168,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -3212,7 +3212,7 @@
         <v>14</v>
       </c>
       <c r="V28" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="W28" t="n">
         <v>13</v>
@@ -3247,7 +3247,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_06.jpg</t>
+          <t>stimuli/flower/flower_30.jpg</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3267,7 +3267,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -3311,7 +3311,7 @@
         <v>9</v>
       </c>
       <c r="V29" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W29" t="n">
         <v>15</v>
@@ -3351,7 +3351,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_34.jpg</t>
+          <t>stimuli/chair/chair_13.jpg</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -3371,7 +3371,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -3413,7 +3413,7 @@
         <v>7</v>
       </c>
       <c r="W30" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="31">
@@ -3445,7 +3445,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_30.jpg</t>
+          <t>stimuli/jacket/jacket_38.jpg</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3465,7 +3465,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -3509,7 +3509,7 @@
         <v>7</v>
       </c>
       <c r="V31" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W31" t="n">
         <v>12</v>
@@ -3539,7 +3539,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_30.jpg</t>
+          <t>stimuli/jacket/jacket_38.jpg</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -3559,7 +3559,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -3605,7 +3605,7 @@
         <v>7</v>
       </c>
       <c r="U32" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="V32" t="n">
         <v>2</v>
@@ -3633,14 +3633,14 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
+          <t>stimuli/jacket/jacket_38.jpg</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
           <t>stimuli/flower/flower_30.jpg</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>stimuli/dog/dog_06.jpg</t>
-        </is>
-      </c>
       <c r="G33" t="inlineStr">
         <is>
           <t>stimuli/fish/fish_40.jpg</t>
@@ -3653,12 +3653,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
+          <t>jacket</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
           <t>flower</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>dog</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -3701,10 +3701,10 @@
         <v>7</v>
       </c>
       <c r="T33" t="n">
+        <v>10</v>
+      </c>
+      <c r="U33" t="n">
         <v>6</v>
-      </c>
-      <c r="U33" t="n">
-        <v>5</v>
       </c>
       <c r="V33" t="n">
         <v>12</v>
@@ -3732,19 +3732,19 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
+          <t>stimuli/flower/flower_30.jpg</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>stimuli/bicycle/bicycle_30.jpg</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
           <t>stimuli/dog/dog_06.jpg</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>stimuli/bicycle/bicycle_30.jpg</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>stimuli/bread/bread_30.jpg</t>
-        </is>
-      </c>
       <c r="H34" t="inlineStr">
         <is>
           <t>stimuli/guitar/guitar_03.jpg</t>
@@ -3752,17 +3752,17 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
+          <t>flower</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
           <t>dog</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>bicycle</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>bread</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -3800,13 +3800,13 @@
         <v>8</v>
       </c>
       <c r="T34" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U34" t="n">
         <v>2</v>
       </c>
       <c r="V34" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="W34" t="n">
         <v>13</v>
@@ -3836,19 +3836,19 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
+          <t>stimuli/bread/bread_30.jpg</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>stimuli/hand/hand_25.jpg</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
           <t>stimuli/jacket/jacket_38.jpg</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>stimuli/hand/hand_25.jpg</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>stimuli/flower/flower_30.jpg</t>
-        </is>
-      </c>
       <c r="I35" t="inlineStr">
         <is>
           <t>bicycle</t>
@@ -3856,17 +3856,17 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
+          <t>bread</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>hand</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
           <t>jacket</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>hand</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>flower</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -3902,13 +3902,13 @@
         <v>2</v>
       </c>
       <c r="U35" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="V35" t="n">
         <v>8</v>
       </c>
       <c r="W35" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="36">
@@ -3930,12 +3930,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_38.jpg</t>
+          <t>stimuli/bread/bread_30.jpg</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_30.jpg</t>
+          <t>stimuli/dog/dog_06.jpg</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -3950,12 +3950,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
@@ -3998,10 +3998,10 @@
         <v>10</v>
       </c>
       <c r="T36" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="U36" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="V36" t="n">
         <v>13</v>
@@ -4029,19 +4029,19 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_30.jpg</t>
+          <t>stimuli/dog/dog_06.jpg</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
+          <t>stimuli/ball/ball_34.jpg</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
           <t>stimuli/chair/chair_13.jpg</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>stimuli/ball/ball_34.jpg</t>
-        </is>
-      </c>
       <c r="H37" t="inlineStr">
         <is>
           <t>stimuli/guitar/guitar_03.jpg</t>
@@ -4049,17 +4049,17 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
+          <t>ball</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
           <t>chair</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>ball</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -4097,13 +4097,13 @@
         <v>11</v>
       </c>
       <c r="T37" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U37" t="n">
+        <v>1</v>
+      </c>
+      <c r="V37" t="n">
         <v>4</v>
-      </c>
-      <c r="V37" t="n">
-        <v>1</v>
       </c>
       <c r="W37" t="n">
         <v>13</v>
@@ -4128,14 +4128,14 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
+          <t>stimuli/ball/ball_34.jpg</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
           <t>stimuli/chair/chair_13.jpg</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>stimuli/ball/ball_34.jpg</t>
-        </is>
-      </c>
       <c r="G38" t="inlineStr">
         <is>
           <t>stimuli/fish/fish_40.jpg</t>
@@ -4143,19 +4143,19 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_38.jpg</t>
+          <t>stimuli/bread/bread_30.jpg</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
+          <t>ball</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
           <t>chair</t>
         </is>
       </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>ball</t>
-        </is>
-      </c>
       <c r="K38" t="inlineStr">
         <is>
           <t>fish</t>
@@ -4163,7 +4163,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -4196,16 +4196,16 @@
         <v>12</v>
       </c>
       <c r="T38" t="n">
+        <v>1</v>
+      </c>
+      <c r="U38" t="n">
         <v>4</v>
-      </c>
-      <c r="U38" t="n">
-        <v>1</v>
       </c>
       <c r="V38" t="n">
         <v>12</v>
       </c>
       <c r="W38" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="39">
@@ -4227,7 +4227,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_34.jpg</t>
+          <t>stimuli/chair/chair_13.jpg</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -4247,7 +4247,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -4295,7 +4295,7 @@
         <v>13</v>
       </c>
       <c r="T39" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U39" t="n">
         <v>15</v>
@@ -4529,7 +4529,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_08.jpg</t>
+          <t>stimuli/jacket/jacket_16.jpg</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -4549,7 +4549,7 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
@@ -4595,7 +4595,7 @@
         <v>15</v>
       </c>
       <c r="U42" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="V42" t="n">
         <v>9</v>
@@ -4623,12 +4623,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_08.jpg</t>
+          <t>stimuli/jacket/jacket_16.jpg</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_05.jpg</t>
+          <t>stimuli/chair/chair_23.jpg</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -4643,12 +4643,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -4691,10 +4691,10 @@
         <v>4</v>
       </c>
       <c r="T43" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="U43" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="V43" t="n">
         <v>7</v>
@@ -4722,19 +4722,19 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
+          <t>stimuli/chair/chair_23.jpg</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>stimuli/bicycle/bicycle_19.jpg</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
           <t>stimuli/ball/ball_05.jpg</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>stimuli/bicycle/bicycle_19.jpg</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>stimuli/chair/chair_23.jpg</t>
-        </is>
-      </c>
       <c r="H44" t="inlineStr">
         <is>
           <t>stimuli/pencil/pencil_31.jpg</t>
@@ -4742,17 +4742,17 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
+          <t>chair</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
           <t>ball</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>bicycle</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>chair</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -4790,13 +4790,13 @@
         <v>5</v>
       </c>
       <c r="T44" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U44" t="n">
         <v>2</v>
       </c>
       <c r="V44" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="W44" t="n">
         <v>16</v>
@@ -4836,7 +4836,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_08.jpg</t>
+          <t>stimuli/jacket/jacket_16.jpg</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -4856,7 +4856,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -4898,7 +4898,7 @@
         <v>14</v>
       </c>
       <c r="W45" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="46">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_37.jpg</t>
+          <t>stimuli/dog/dog_09.jpg</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_09.jpg</t>
+          <t>stimuli/flower/flower_08.jpg</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -4945,12 +4945,12 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -4991,10 +4991,10 @@
         <v>9</v>
       </c>
       <c r="U46" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="V46" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W46" t="n">
         <v>8</v>
@@ -5019,19 +5019,19 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
+          <t>stimuli/dog/dog_09.jpg</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>stimuli/flower/flower_08.jpg</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
           <t>stimuli/bread/bread_37.jpg</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>stimuli/dog/dog_09.jpg</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>stimuli/jacket/jacket_16.jpg</t>
-        </is>
-      </c>
       <c r="H47" t="inlineStr">
         <is>
           <t>stimuli/pencil/pencil_31.jpg</t>
@@ -5039,17 +5039,17 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
+          <t>dog</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>flower</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
           <t>bread</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>dog</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>jacket</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -5087,13 +5087,13 @@
         <v>8</v>
       </c>
       <c r="T47" t="n">
+        <v>5</v>
+      </c>
+      <c r="U47" t="n">
+        <v>6</v>
+      </c>
+      <c r="V47" t="n">
         <v>3</v>
-      </c>
-      <c r="U47" t="n">
-        <v>5</v>
-      </c>
-      <c r="V47" t="n">
-        <v>10</v>
       </c>
       <c r="W47" t="n">
         <v>16</v>
@@ -5118,7 +5118,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_09.jpg</t>
+          <t>stimuli/flower/flower_08.jpg</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -5128,17 +5128,17 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
+          <t>stimuli/ball/ball_05.jpg</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
           <t>stimuli/chair/chair_23.jpg</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>stimuli/ball/ball_05.jpg</t>
-        </is>
-      </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -5148,12 +5148,12 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
+          <t>ball</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
           <t>chair</t>
-        </is>
-      </c>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>ball</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -5186,16 +5186,16 @@
         <v>9</v>
       </c>
       <c r="T48" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U48" t="n">
         <v>7</v>
       </c>
       <c r="V48" t="n">
+        <v>1</v>
+      </c>
+      <c r="W48" t="n">
         <v>4</v>
-      </c>
-      <c r="W48" t="n">
-        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -5222,7 +5222,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_23.jpg</t>
+          <t>stimuli/ball/ball_05.jpg</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -5242,7 +5242,7 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -5288,7 +5288,7 @@
         <v>7</v>
       </c>
       <c r="U49" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="V49" t="n">
         <v>15</v>
@@ -5316,12 +5316,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_23.jpg</t>
+          <t>stimuli/ball/ball_05.jpg</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_16.jpg</t>
+          <t>stimuli/bread/bread_37.jpg</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -5331,17 +5331,17 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_37.jpg</t>
+          <t>stimuli/dog/dog_09.jpg</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -5384,16 +5384,16 @@
         <v>11</v>
       </c>
       <c r="T50" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U50" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="V50" t="n">
         <v>14</v>
       </c>
       <c r="W50" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="51">
@@ -5415,7 +5415,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_16.jpg</t>
+          <t>stimuli/bread/bread_37.jpg</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_09.jpg</t>
+          <t>stimuli/flower/flower_08.jpg</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -5450,7 +5450,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -5483,7 +5483,7 @@
         <v>12</v>
       </c>
       <c r="T51" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="U51" t="n">
         <v>8</v>
@@ -5492,7 +5492,7 @@
         <v>11</v>
       </c>
       <c r="W51" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="52">
@@ -5529,7 +5529,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_05.jpg</t>
+          <t>stimuli/chair/chair_23.jpg</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -5549,7 +5549,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -5591,7 +5591,7 @@
         <v>14</v>
       </c>
       <c r="W52" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="53">
@@ -5623,7 +5623,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_08.jpg</t>
+          <t>stimuli/jacket/jacket_16.jpg</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -5643,7 +5643,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -5687,7 +5687,7 @@
         <v>11</v>
       </c>
       <c r="V53" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W53" t="n">
         <v>14</v>
@@ -5821,7 +5821,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_06.jpg</t>
+          <t>stimuli/flower/flower_30.jpg</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -5841,7 +5841,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -5885,7 +5885,7 @@
         <v>9</v>
       </c>
       <c r="V55" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W55" t="n">
         <v>13</v>
@@ -5920,7 +5920,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_38.jpg</t>
+          <t>stimuli/bread/bread_30.jpg</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -5940,7 +5940,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -5984,7 +5984,7 @@
         <v>8</v>
       </c>
       <c r="V56" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="W56" t="n">
         <v>15</v>
@@ -6019,7 +6019,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_13.jpg</t>
+          <t>stimuli/ball/ball_34.jpg</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -6039,7 +6039,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -6083,7 +6083,7 @@
         <v>7</v>
       </c>
       <c r="V57" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="W57" t="n">
         <v>13</v>
@@ -6113,7 +6113,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_30.jpg</t>
+          <t>stimuli/jacket/jacket_38.jpg</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -6133,7 +6133,7 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -6179,7 +6179,7 @@
         <v>7</v>
       </c>
       <c r="U58" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="V58" t="n">
         <v>2</v>
@@ -6207,17 +6207,17 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
+          <t>stimuli/jacket/jacket_38.jpg</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
           <t>stimuli/flower/flower_30.jpg</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>stimuli/dog/dog_06.jpg</t>
-        </is>
-      </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_34.jpg</t>
+          <t>stimuli/chair/chair_13.jpg</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -6227,17 +6227,17 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
+          <t>jacket</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
           <t>flower</t>
         </is>
       </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>dog</t>
-        </is>
-      </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -6275,13 +6275,13 @@
         <v>7</v>
       </c>
       <c r="T59" t="n">
+        <v>10</v>
+      </c>
+      <c r="U59" t="n">
         <v>6</v>
       </c>
-      <c r="U59" t="n">
-        <v>5</v>
-      </c>
       <c r="V59" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="W59" t="n">
         <v>13</v>
@@ -6306,7 +6306,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_06.jpg</t>
+          <t>stimuli/flower/flower_30.jpg</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -6326,7 +6326,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -6374,7 +6374,7 @@
         <v>8</v>
       </c>
       <c r="T60" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U60" t="n">
         <v>2</v>
@@ -6410,12 +6410,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_38.jpg</t>
+          <t>stimuli/bread/bread_30.jpg</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_30.jpg</t>
+          <t>stimuli/dog/dog_06.jpg</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -6430,12 +6430,12 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -6476,10 +6476,10 @@
         <v>2</v>
       </c>
       <c r="U61" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="V61" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="W61" t="n">
         <v>15</v>
@@ -6504,42 +6504,42 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
+          <t>stimuli/bread/bread_30.jpg</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>stimuli/dog/dog_06.jpg</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>stimuli/hand/hand_25.jpg</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
           <t>stimuli/jacket/jacket_38.jpg</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>stimuli/bread/bread_30.jpg</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>stimuli/hand/hand_25.jpg</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>stimuli/flower/flower_30.jpg</t>
-        </is>
-      </c>
       <c r="I62" t="inlineStr">
         <is>
+          <t>bread</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>dog</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>hand</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
           <t>jacket</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>bread</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>hand</t>
-        </is>
-      </c>
-      <c r="L62" t="inlineStr">
-        <is>
-          <t>flower</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
@@ -6572,16 +6572,16 @@
         <v>10</v>
       </c>
       <c r="T62" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="U62" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="V62" t="n">
         <v>8</v>
       </c>
       <c r="W62" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="63">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_30.jpg</t>
+          <t>stimuli/dog/dog_06.jpg</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_13.jpg</t>
+          <t>stimuli/ball/ball_34.jpg</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -6618,17 +6618,17 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_06.jpg</t>
+          <t>stimuli/flower/flower_30.jpg</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -6638,7 +6638,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -6671,16 +6671,16 @@
         <v>11</v>
       </c>
       <c r="T63" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U63" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="V63" t="n">
         <v>14</v>
       </c>
       <c r="W63" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="64">
@@ -6702,14 +6702,14 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
+          <t>stimuli/ball/ball_34.jpg</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
           <t>stimuli/chair/chair_13.jpg</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>stimuli/ball/ball_34.jpg</t>
-        </is>
-      </c>
       <c r="G64" t="inlineStr">
         <is>
           <t>stimuli/house/house_44.jpg</t>
@@ -6717,19 +6717,19 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_30.jpg</t>
+          <t>stimuli/jacket/jacket_38.jpg</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
+          <t>ball</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
           <t>chair</t>
         </is>
       </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>ball</t>
-        </is>
-      </c>
       <c r="K64" t="inlineStr">
         <is>
           <t>house</t>
@@ -6737,7 +6737,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -6770,16 +6770,16 @@
         <v>12</v>
       </c>
       <c r="T64" t="n">
+        <v>1</v>
+      </c>
+      <c r="U64" t="n">
         <v>4</v>
-      </c>
-      <c r="U64" t="n">
-        <v>1</v>
       </c>
       <c r="V64" t="n">
         <v>9</v>
       </c>
       <c r="W64" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="65">
@@ -6801,7 +6801,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_34.jpg</t>
+          <t>stimuli/chair/chair_13.jpg</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -6821,7 +6821,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -6869,7 +6869,7 @@
         <v>13</v>
       </c>
       <c r="T65" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U65" t="n">
         <v>15</v>
@@ -6915,7 +6915,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_13.jpg</t>
+          <t>stimuli/ball/ball_34.jpg</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -6935,7 +6935,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
@@ -6977,7 +6977,7 @@
         <v>14</v>
       </c>
       <c r="W66" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -7009,7 +7009,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_09.jpg</t>
+          <t>stimuli/flower/flower_08.jpg</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -7029,7 +7029,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -7073,7 +7073,7 @@
         <v>15</v>
       </c>
       <c r="V67" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W67" t="n">
         <v>11</v>
@@ -7103,7 +7103,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_08.jpg</t>
+          <t>stimuli/jacket/jacket_16.jpg</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
@@ -7169,7 +7169,7 @@
         <v>15</v>
       </c>
       <c r="U68" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="V68" t="n">
         <v>2</v>
@@ -7197,19 +7197,19 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_08.jpg</t>
+          <t>stimuli/jacket/jacket_16.jpg</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
+          <t>stimuli/chair/chair_23.jpg</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
           <t>stimuli/ball/ball_05.jpg</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>stimuli/chair/chair_23.jpg</t>
-        </is>
-      </c>
       <c r="H69" t="inlineStr">
         <is>
           <t>stimuli/car/car_01.jpg</t>
@@ -7217,17 +7217,17 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
+          <t>chair</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
           <t>ball</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>chair</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -7265,13 +7265,13 @@
         <v>4</v>
       </c>
       <c r="T69" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="U69" t="n">
+        <v>4</v>
+      </c>
+      <c r="V69" t="n">
         <v>1</v>
-      </c>
-      <c r="V69" t="n">
-        <v>4</v>
       </c>
       <c r="W69" t="n">
         <v>11</v>
@@ -7296,7 +7296,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_05.jpg</t>
+          <t>stimuli/chair/chair_23.jpg</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -7306,7 +7306,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_16.jpg</t>
+          <t>stimuli/bread/bread_37.jpg</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -7316,7 +7316,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -7326,7 +7326,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -7364,13 +7364,13 @@
         <v>5</v>
       </c>
       <c r="T70" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U70" t="n">
         <v>2</v>
       </c>
       <c r="V70" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="W70" t="n">
         <v>16</v>
@@ -7410,7 +7410,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_16.jpg</t>
+          <t>stimuli/bread/bread_37.jpg</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -7430,7 +7430,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -7472,7 +7472,7 @@
         <v>7</v>
       </c>
       <c r="W71" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="72">
@@ -7499,7 +7499,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_37.jpg</t>
+          <t>stimuli/dog/dog_09.jpg</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -7509,7 +7509,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_05.jpg</t>
+          <t>stimuli/chair/chair_23.jpg</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -7519,7 +7519,7 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
@@ -7529,7 +7529,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -7565,13 +7565,13 @@
         <v>9</v>
       </c>
       <c r="U72" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="V72" t="n">
         <v>14</v>
       </c>
       <c r="W72" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="73">
@@ -7593,17 +7593,17 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_37.jpg</t>
+          <t>stimuli/dog/dog_09.jpg</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_09.jpg</t>
+          <t>stimuli/flower/flower_08.jpg</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_23.jpg</t>
+          <t>stimuli/ball/ball_05.jpg</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -7613,17 +7613,17 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -7661,13 +7661,13 @@
         <v>8</v>
       </c>
       <c r="T73" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U73" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V73" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="W73" t="n">
         <v>8</v>
@@ -7692,7 +7692,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_09.jpg</t>
+          <t>stimuli/flower/flower_08.jpg</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -7712,7 +7712,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -7760,7 +7760,7 @@
         <v>9</v>
       </c>
       <c r="T74" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U74" t="n">
         <v>7</v>
@@ -7796,12 +7796,12 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_23.jpg</t>
+          <t>stimuli/ball/ball_05.jpg</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_16.jpg</t>
+          <t>stimuli/bread/bread_37.jpg</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -7816,12 +7816,12 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -7862,10 +7862,10 @@
         <v>7</v>
       </c>
       <c r="U75" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="V75" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="W75" t="n">
         <v>9</v>
@@ -7890,19 +7890,19 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_23.jpg</t>
+          <t>stimuli/ball/ball_05.jpg</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
+          <t>stimuli/bread/bread_37.jpg</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
           <t>stimuli/jacket/jacket_16.jpg</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>stimuli/flower/flower_08.jpg</t>
-        </is>
-      </c>
       <c r="H76" t="inlineStr">
         <is>
           <t>stimuli/bicycle/bicycle_19.jpg</t>
@@ -7910,17 +7910,17 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
+          <t>bread</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
           <t>jacket</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>flower</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -7958,13 +7958,13 @@
         <v>11</v>
       </c>
       <c r="T76" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U76" t="n">
+        <v>3</v>
+      </c>
+      <c r="V76" t="n">
         <v>10</v>
-      </c>
-      <c r="V76" t="n">
-        <v>6</v>
       </c>
       <c r="W76" t="n">
         <v>2</v>
@@ -7989,7 +7989,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_16.jpg</t>
+          <t>stimuli/bread/bread_37.jpg</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -8004,12 +8004,12 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_37.jpg</t>
+          <t>stimuli/dog/dog_09.jpg</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -8024,7 +8024,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
@@ -8057,7 +8057,7 @@
         <v>12</v>
       </c>
       <c r="T77" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="U77" t="n">
         <v>8</v>
@@ -8066,7 +8066,7 @@
         <v>15</v>
       </c>
       <c r="W77" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="78">
@@ -8197,12 +8197,12 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_08.jpg</t>
+          <t>stimuli/jacket/jacket_16.jpg</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_23.jpg</t>
+          <t>stimuli/ball/ball_05.jpg</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -8217,12 +8217,12 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
@@ -8261,10 +8261,10 @@
         <v>11</v>
       </c>
       <c r="V79" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W79" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="80">
@@ -8395,7 +8395,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_30.jpg</t>
+          <t>stimuli/jacket/jacket_38.jpg</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -8415,7 +8415,7 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -8459,7 +8459,7 @@
         <v>9</v>
       </c>
       <c r="V81" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W81" t="n">
         <v>13</v>
@@ -8494,7 +8494,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_13.jpg</t>
+          <t>stimuli/ball/ball_34.jpg</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -8514,7 +8514,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -8558,7 +8558,7 @@
         <v>8</v>
       </c>
       <c r="V82" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="W82" t="n">
         <v>15</v>
@@ -8593,7 +8593,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_38.jpg</t>
+          <t>stimuli/bread/bread_30.jpg</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -8613,7 +8613,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -8657,7 +8657,7 @@
         <v>7</v>
       </c>
       <c r="V83" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="W83" t="n">
         <v>13</v>
@@ -8687,7 +8687,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_30.jpg</t>
+          <t>stimuli/jacket/jacket_38.jpg</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -8707,7 +8707,7 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -8753,7 +8753,7 @@
         <v>7</v>
       </c>
       <c r="U84" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="V84" t="n">
         <v>2</v>
@@ -8781,17 +8781,17 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
+          <t>stimuli/jacket/jacket_38.jpg</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
           <t>stimuli/flower/flower_30.jpg</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>stimuli/dog/dog_06.jpg</t>
-        </is>
-      </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_34.jpg</t>
+          <t>stimuli/chair/chair_13.jpg</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -8801,17 +8801,17 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
+          <t>jacket</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
           <t>flower</t>
         </is>
       </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>dog</t>
-        </is>
-      </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -8849,13 +8849,13 @@
         <v>7</v>
       </c>
       <c r="T85" t="n">
+        <v>10</v>
+      </c>
+      <c r="U85" t="n">
         <v>6</v>
       </c>
-      <c r="U85" t="n">
-        <v>5</v>
-      </c>
       <c r="V85" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="W85" t="n">
         <v>13</v>
@@ -8880,19 +8880,19 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
+          <t>stimuli/flower/flower_30.jpg</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>stimuli/bicycle/bicycle_30.jpg</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
           <t>stimuli/dog/dog_06.jpg</t>
         </is>
       </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>stimuli/bicycle/bicycle_30.jpg</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>stimuli/bread/bread_30.jpg</t>
-        </is>
-      </c>
       <c r="H86" t="inlineStr">
         <is>
           <t>stimuli/key/key_35.jpg</t>
@@ -8900,17 +8900,17 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
+          <t>flower</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>bicycle</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
           <t>dog</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>bicycle</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>bread</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -8948,13 +8948,13 @@
         <v>8</v>
       </c>
       <c r="T86" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U86" t="n">
         <v>2</v>
       </c>
       <c r="V86" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="W86" t="n">
         <v>15</v>
@@ -8984,7 +8984,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_38.jpg</t>
+          <t>stimuli/bread/bread_30.jpg</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -9004,7 +9004,7 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -9050,7 +9050,7 @@
         <v>2</v>
       </c>
       <c r="U87" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="V87" t="n">
         <v>14</v>
@@ -9078,12 +9078,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_38.jpg</t>
+          <t>stimuli/bread/bread_30.jpg</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_30.jpg</t>
+          <t>stimuli/dog/dog_06.jpg</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -9093,17 +9093,17 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_06.jpg</t>
+          <t>stimuli/flower/flower_30.jpg</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -9113,7 +9113,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
@@ -9146,16 +9146,16 @@
         <v>10</v>
       </c>
       <c r="T88" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="U88" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="V88" t="n">
         <v>15</v>
       </c>
       <c r="W88" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="89">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_30.jpg</t>
+          <t>stimuli/dog/dog_06.jpg</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_13.jpg</t>
+          <t>stimuli/ball/ball_34.jpg</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -9192,17 +9192,17 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_30.jpg</t>
+          <t>stimuli/jacket/jacket_38.jpg</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -9212,7 +9212,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
@@ -9245,16 +9245,16 @@
         <v>11</v>
       </c>
       <c r="T89" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U89" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="V89" t="n">
         <v>8</v>
       </c>
       <c r="W89" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="90">
@@ -9276,14 +9276,14 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
+          <t>stimuli/ball/ball_34.jpg</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
           <t>stimuli/chair/chair_13.jpg</t>
         </is>
       </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>stimuli/ball/ball_34.jpg</t>
-        </is>
-      </c>
       <c r="G90" t="inlineStr">
         <is>
           <t>stimuli/house/house_44.jpg</t>
@@ -9291,19 +9291,19 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_06.jpg</t>
+          <t>stimuli/flower/flower_30.jpg</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
+          <t>ball</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
           <t>chair</t>
         </is>
       </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>ball</t>
-        </is>
-      </c>
       <c r="K90" t="inlineStr">
         <is>
           <t>house</t>
@@ -9311,7 +9311,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
@@ -9344,16 +9344,16 @@
         <v>12</v>
       </c>
       <c r="T90" t="n">
+        <v>1</v>
+      </c>
+      <c r="U90" t="n">
         <v>4</v>
-      </c>
-      <c r="U90" t="n">
-        <v>1</v>
       </c>
       <c r="V90" t="n">
         <v>9</v>
       </c>
       <c r="W90" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="91">
@@ -9375,7 +9375,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_34.jpg</t>
+          <t>stimuli/chair/chair_13.jpg</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -9390,12 +9390,12 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_30.jpg</t>
+          <t>stimuli/jacket/jacket_38.jpg</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -9410,7 +9410,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
@@ -9443,7 +9443,7 @@
         <v>13</v>
       </c>
       <c r="T91" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U91" t="n">
         <v>15</v>
@@ -9452,7 +9452,7 @@
         <v>12</v>
       </c>
       <c r="W91" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="92">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_08.jpg</t>
+          <t>stimuli/jacket/jacket_16.jpg</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_05.jpg</t>
+          <t>stimuli/chair/chair_23.jpg</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -9697,12 +9697,12 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
@@ -9743,10 +9743,10 @@
         <v>15</v>
       </c>
       <c r="U94" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="V94" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="W94" t="n">
         <v>8</v>
@@ -9771,12 +9771,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_08.jpg</t>
+          <t>stimuli/jacket/jacket_16.jpg</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_05.jpg</t>
+          <t>stimuli/chair/chair_23.jpg</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -9791,12 +9791,12 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -9839,10 +9839,10 @@
         <v>4</v>
       </c>
       <c r="T95" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="U95" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="V95" t="n">
         <v>2</v>
@@ -9870,7 +9870,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>stimuli/ball/ball_05.jpg</t>
+          <t>stimuli/chair/chair_23.jpg</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -9890,7 +9890,7 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>ball</t>
+          <t>chair</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
@@ -9938,7 +9938,7 @@
         <v>5</v>
       </c>
       <c r="T96" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U96" t="n">
         <v>2</v>
@@ -9979,7 +9979,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_09.jpg</t>
+          <t>stimuli/flower/flower_08.jpg</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -9999,7 +9999,7 @@
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -10043,7 +10043,7 @@
         <v>9</v>
       </c>
       <c r="V97" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W97" t="n">
         <v>8</v>
@@ -10073,19 +10073,19 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
+          <t>stimuli/dog/dog_09.jpg</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>stimuli/hammer/hammer_02.jpg</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
           <t>stimuli/bread/bread_37.jpg</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>stimuli/hammer/hammer_02.jpg</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>stimuli/jacket/jacket_16.jpg</t>
-        </is>
-      </c>
       <c r="I98" t="inlineStr">
         <is>
           <t>house</t>
@@ -10093,17 +10093,17 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
+          <t>dog</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>hammer</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
           <t>bread</t>
-        </is>
-      </c>
-      <c r="K98" t="inlineStr">
-        <is>
-          <t>hammer</t>
-        </is>
-      </c>
-      <c r="L98" t="inlineStr">
-        <is>
-          <t>jacket</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
@@ -10139,13 +10139,13 @@
         <v>9</v>
       </c>
       <c r="U98" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="V98" t="n">
         <v>7</v>
       </c>
       <c r="W98" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="99">
@@ -10167,17 +10167,17 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_37.jpg</t>
+          <t>stimuli/dog/dog_09.jpg</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_09.jpg</t>
+          <t>stimuli/flower/flower_08.jpg</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_23.jpg</t>
+          <t>stimuli/ball/ball_05.jpg</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -10187,17 +10187,17 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -10235,13 +10235,13 @@
         <v>8</v>
       </c>
       <c r="T99" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="U99" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V99" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="W99" t="n">
         <v>16</v>
@@ -10266,7 +10266,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>stimuli/dog/dog_09.jpg</t>
+          <t>stimuli/flower/flower_08.jpg</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -10276,7 +10276,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>stimuli/flower/flower_08.jpg</t>
+          <t>stimuli/jacket/jacket_16.jpg</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -10286,7 +10286,7 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>dog</t>
+          <t>flower</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -10296,7 +10296,7 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>flower</t>
+          <t>jacket</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -10334,13 +10334,13 @@
         <v>9</v>
       </c>
       <c r="T100" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U100" t="n">
         <v>7</v>
       </c>
       <c r="V100" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="W100" t="n">
         <v>2</v>
@@ -10370,7 +10370,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>stimuli/chair/chair_23.jpg</t>
+          <t>stimuli/ball/ball_05.jpg</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -10380,7 +10380,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_37.jpg</t>
+          <t>stimuli/dog/dog_09.jpg</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -10390,7 +10390,7 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>chair</t>
+          <t>ball</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -10400,7 +10400,7 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
@@ -10436,13 +10436,13 @@
         <v>7</v>
       </c>
       <c r="U101" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="V101" t="n">
         <v>2</v>
       </c>
       <c r="W101" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="102">
@@ -10464,42 +10464,42 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
+          <t>stimuli/ball/ball_05.jpg</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>stimuli/bread/bread_37.jpg</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>stimuli/key/key_12.jpg</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
           <t>stimuli/chair/chair_23.jpg</t>
         </is>
       </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>stimuli/jacket/jacket_16.jpg</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>stimuli/key/key_12.jpg</t>
-        </is>
-      </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>stimuli/ball/ball_05.jpg</t>
-        </is>
-      </c>
       <c r="I102" t="inlineStr">
         <is>
+          <t>ball</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>bread</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>key</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
           <t>chair</t>
-        </is>
-      </c>
-      <c r="J102" t="inlineStr">
-        <is>
-          <t>jacket</t>
-        </is>
-      </c>
-      <c r="K102" t="inlineStr">
-        <is>
-          <t>key</t>
-        </is>
-      </c>
-      <c r="L102" t="inlineStr">
-        <is>
-          <t>ball</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
@@ -10532,16 +10532,16 @@
         <v>11</v>
       </c>
       <c r="T102" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U102" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="V102" t="n">
         <v>15</v>
       </c>
       <c r="W102" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="103">
@@ -10563,7 +10563,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>stimuli/jacket/jacket_16.jpg</t>
+          <t>stimuli/bread/bread_37.jpg</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -10583,7 +10583,7 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>jacket</t>
+          <t>bread</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -10631,7 +10631,7 @@
         <v>12</v>
       </c>
       <c r="T103" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="U103" t="n">
         <v>8</v>
@@ -10672,14 +10672,14 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
+          <t>stimuli/chair/chair_23.jpg</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
           <t>stimuli/ball/ball_05.jpg</t>
         </is>
       </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>stimuli/chair/chair_23.jpg</t>
-        </is>
-      </c>
       <c r="I104" t="inlineStr">
         <is>
           <t>hand</t>
@@ -10692,12 +10692,12 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
+          <t>chair</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
           <t>ball</t>
-        </is>
-      </c>
-      <c r="L104" t="inlineStr">
-        <is>
-          <t>chair</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
@@ -10736,10 +10736,10 @@
         <v>16</v>
       </c>
       <c r="V104" t="n">
+        <v>4</v>
+      </c>
+      <c r="W104" t="n">
         <v>1</v>
-      </c>
-      <c r="W104" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="105">
@@ -10771,7 +10771,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>stimuli/bread/bread_37.jpg</t>
+          <t>stimuli/dog/dog_09.jpg</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -10791,7 +10791,7 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>bread</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -10835,7 +10835,7 @@
         <v>11</v>
       </c>
       <c r="V105" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="W105" t="n">
         <v>14</v>
